--- a/artfynd/A 19827-2025 artfynd.xlsx
+++ b/artfynd/A 19827-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1693,6 +1693,113 @@
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>126435624</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57656</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Fisklössjöflon, Mpd</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>593742</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6972859</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 19827-2025 artfynd.xlsx
+++ b/artfynd/A 19827-2025 artfynd.xlsx
@@ -1698,7 +1698,7 @@
         <v>126435624</v>
       </c>
       <c r="B12" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 19827-2025 artfynd.xlsx
+++ b/artfynd/A 19827-2025 artfynd.xlsx
@@ -1698,7 +1698,7 @@
         <v>126435624</v>
       </c>
       <c r="B12" t="n">
-        <v>57657</v>
+        <v>57736</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 19827-2025 artfynd.xlsx
+++ b/artfynd/A 19827-2025 artfynd.xlsx
@@ -1698,7 +1698,7 @@
         <v>126435624</v>
       </c>
       <c r="B12" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 19827-2025 artfynd.xlsx
+++ b/artfynd/A 19827-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117192058</v>
+        <v>117192052</v>
       </c>
       <c r="B2" t="n">
-        <v>79527</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>593564</v>
+        <v>593729</v>
       </c>
       <c r="R2" t="n">
-        <v>6972940</v>
+        <v>6972876</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117192057</v>
+        <v>117192053</v>
       </c>
       <c r="B3" t="n">
-        <v>79527</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81312</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>1049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +807,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593613</v>
+        <v>593615</v>
       </c>
       <c r="R3" t="n">
-        <v>6972956</v>
+        <v>6972885</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117192053</v>
+        <v>117192060</v>
       </c>
       <c r="B4" t="n">
-        <v>80403</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1049</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593615</v>
+        <v>593512</v>
       </c>
       <c r="R4" t="n">
-        <v>6972885</v>
+        <v>6972928</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -981,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117192056</v>
+        <v>117192059</v>
       </c>
       <c r="B5" t="n">
-        <v>78446</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -997,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,13 +1001,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>593611</v>
+        <v>593546</v>
       </c>
       <c r="R5" t="n">
-        <v>6972923</v>
+        <v>6972911</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1083,15 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117192061</v>
+        <v>117192055</v>
       </c>
       <c r="B6" t="n">
-        <v>79035</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91962</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1099,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229821</v>
+        <v>2079</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,13 +1098,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>593440</v>
+        <v>593615</v>
       </c>
       <c r="R6" t="n">
-        <v>6972965</v>
+        <v>6972904</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1185,37 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117192055</v>
+        <v>117192056</v>
       </c>
       <c r="B7" t="n">
-        <v>91928</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,13 +1195,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>593615</v>
+        <v>593611</v>
       </c>
       <c r="R7" t="n">
-        <v>6972904</v>
+        <v>6972923</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1287,15 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117192059</v>
+        <v>117192054</v>
       </c>
       <c r="B8" t="n">
-        <v>82225</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1303,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,13 +1292,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>593546</v>
+        <v>593614</v>
       </c>
       <c r="R8" t="n">
-        <v>6972911</v>
+        <v>6972884</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1389,15 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117192052</v>
+        <v>117192057</v>
       </c>
       <c r="B9" t="n">
-        <v>78480</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1405,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>593729</v>
+        <v>593613</v>
       </c>
       <c r="R9" t="n">
-        <v>6972876</v>
+        <v>6972956</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,15 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117192060</v>
+        <v>117192058</v>
       </c>
       <c r="B10" t="n">
-        <v>90465</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1507,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,13 +1486,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>593512</v>
+        <v>593564</v>
       </c>
       <c r="R10" t="n">
-        <v>6972928</v>
+        <v>6972940</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1593,15 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117192054</v>
+        <v>126435624</v>
       </c>
       <c r="B11" t="n">
-        <v>79064</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1609,34 +1559,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Fisklössjön, Mpd</t>
+          <t>Fisklössjöflon, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>593614</v>
+        <v>593742</v>
       </c>
       <c r="R11" t="n">
-        <v>6972884</v>
+        <v>6972859</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1663,12 +1618,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-05-17</t>
+          <t>2025-07-05</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-05-17</t>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1683,22 +1643,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126435624</v>
+        <v>117192061</v>
       </c>
       <c r="B12" t="n">
-        <v>57741</v>
+        <v>79917</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1706,39 +1666,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Fisklössjöflon, Mpd</t>
+          <t>Fisklössjön, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>593742</v>
+        <v>593440</v>
       </c>
       <c r="R12" t="n">
-        <v>6972859</v>
+        <v>6972965</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1765,17 +1720,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-07-05</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-07-05</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1790,12 +1740,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 19827-2025 artfynd.xlsx
+++ b/artfynd/A 19827-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117192052</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117192053</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117192060</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117192059</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117192055</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117192056</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117192054</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117192057</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117192058</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1652,6 +1702,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126435624</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1749,8 +1804,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117192061</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>